--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R381"/>
+  <dimension ref="A1:R384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23182,7 +23182,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>351.02</v>
+        <v>357.21</v>
       </c>
       <c r="C381" t="n">
         <v>317.1</v>
@@ -23203,13 +23203,13 @@
         <v>323.73</v>
       </c>
       <c r="I381" t="n">
-        <v>331.67</v>
+        <v>324.94</v>
       </c>
       <c r="J381" t="n">
-        <v>334.68</v>
+        <v>327.03</v>
       </c>
       <c r="K381" t="n">
-        <v>337.72</v>
+        <v>331.74</v>
       </c>
       <c r="L381" t="n">
         <v>325.15</v>
@@ -23230,6 +23230,186 @@
         <v>360.83</v>
       </c>
       <c r="R381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>355.88</v>
+      </c>
+      <c r="C382" t="n">
+        <v>317.59</v>
+      </c>
+      <c r="D382" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="E382" t="n">
+        <v>299.13</v>
+      </c>
+      <c r="F382" t="n">
+        <v>317.96</v>
+      </c>
+      <c r="G382" t="n">
+        <v>331.4</v>
+      </c>
+      <c r="H382" t="n">
+        <v>322.37</v>
+      </c>
+      <c r="I382" t="n">
+        <v>323.21</v>
+      </c>
+      <c r="J382" t="n">
+        <v>326.09</v>
+      </c>
+      <c r="K382" t="n">
+        <v>329.66</v>
+      </c>
+      <c r="L382" t="n">
+        <v>325.15</v>
+      </c>
+      <c r="M382" t="n">
+        <v>341.92</v>
+      </c>
+      <c r="N382" t="n">
+        <v>336.06</v>
+      </c>
+      <c r="O382" t="n">
+        <v>340.29</v>
+      </c>
+      <c r="P382" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="Q382" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="n">
+        <v>355.88</v>
+      </c>
+      <c r="C383" t="n">
+        <v>317.59</v>
+      </c>
+      <c r="D383" t="n">
+        <v>308.63</v>
+      </c>
+      <c r="E383" t="n">
+        <v>298.52</v>
+      </c>
+      <c r="F383" t="n">
+        <v>319.72</v>
+      </c>
+      <c r="G383" t="n">
+        <v>332.43</v>
+      </c>
+      <c r="H383" t="n">
+        <v>322.73</v>
+      </c>
+      <c r="I383" t="n">
+        <v>324.01</v>
+      </c>
+      <c r="J383" t="n">
+        <v>327.18</v>
+      </c>
+      <c r="K383" t="n">
+        <v>329.79</v>
+      </c>
+      <c r="L383" t="n">
+        <v>325.15</v>
+      </c>
+      <c r="M383" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="N383" t="n">
+        <v>331.55</v>
+      </c>
+      <c r="O383" t="n">
+        <v>336.28</v>
+      </c>
+      <c r="P383" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="Q383" t="n">
+        <v>358.29</v>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>355.82</v>
+      </c>
+      <c r="C384" t="n">
+        <v>318.38</v>
+      </c>
+      <c r="D384" t="n">
+        <v>308.8</v>
+      </c>
+      <c r="E384" t="n">
+        <v>299.14</v>
+      </c>
+      <c r="F384" t="n">
+        <v>320.16</v>
+      </c>
+      <c r="G384" t="n">
+        <v>332.23</v>
+      </c>
+      <c r="H384" t="n">
+        <v>322.85</v>
+      </c>
+      <c r="I384" t="n">
+        <v>322.96</v>
+      </c>
+      <c r="J384" t="n">
+        <v>326.03</v>
+      </c>
+      <c r="K384" t="n">
+        <v>328.77</v>
+      </c>
+      <c r="L384" t="n">
+        <v>321.41</v>
+      </c>
+      <c r="M384" t="n">
+        <v>338.88</v>
+      </c>
+      <c r="N384" t="n">
+        <v>331.69</v>
+      </c>
+      <c r="O384" t="n">
+        <v>336.76</v>
+      </c>
+      <c r="P384" t="n">
+        <v>346.75</v>
+      </c>
+      <c r="Q384" t="n">
+        <v>357.2</v>
+      </c>
+      <c r="R384" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -23246,7 +23426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B406"/>
+  <dimension ref="A1:B409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27309,6 +27489,36 @@
       </c>
       <c r="B406" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B407" t="n">
+        <v>0.71</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B408" t="n">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B409" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -27477,28 +27687,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007499496891259405</v>
+        <v>0.008468362930902454</v>
       </c>
       <c r="J2" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>3.201502429728276e-05</v>
+        <v>4.11634419776874e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.772339793858403</v>
+        <v>7.788792142276868</v>
       </c>
       <c r="N2" t="n">
-        <v>97.02303307595054</v>
+        <v>97.03222283920763</v>
       </c>
       <c r="O2" t="n">
-        <v>9.850027059655751</v>
+        <v>9.85049353277325</v>
       </c>
       <c r="P2" t="n">
-        <v>347.5305123074702</v>
+        <v>347.3531042057033</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27555,28 +27765,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0221405088643405</v>
+        <v>-0.0199360353549694</v>
       </c>
       <c r="J3" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K3" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0005574467205792244</v>
+        <v>0.0004592952850019927</v>
       </c>
       <c r="M3" t="n">
-        <v>5.345602774241318</v>
+        <v>5.313460335921629</v>
       </c>
       <c r="N3" t="n">
-        <v>48.54091921332757</v>
+        <v>48.17621797752595</v>
       </c>
       <c r="O3" t="n">
-        <v>6.967131347500747</v>
+        <v>6.940909016658117</v>
       </c>
       <c r="P3" t="n">
-        <v>316.9876739698382</v>
+        <v>316.9631633991543</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27633,28 +27843,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.276537076483741</v>
+        <v>-0.2646337492100172</v>
       </c>
       <c r="J4" t="n">
+        <v>383</v>
+      </c>
+      <c r="K4" t="n">
         <v>380</v>
       </c>
-      <c r="K4" t="n">
-        <v>377</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.04436017349177002</v>
+        <v>0.04121431705314738</v>
       </c>
       <c r="M4" t="n">
-        <v>6.742054447054457</v>
+        <v>6.759778957323602</v>
       </c>
       <c r="N4" t="n">
-        <v>90.13395167108226</v>
+        <v>89.89463079220376</v>
       </c>
       <c r="O4" t="n">
-        <v>9.493890228514456</v>
+        <v>9.48127790923796</v>
       </c>
       <c r="P4" t="n">
-        <v>308.3273316544892</v>
+        <v>308.1941696503703</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27711,28 +27921,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0638455934565265</v>
+        <v>0.06258558242572268</v>
       </c>
       <c r="J5" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K5" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001048777041719906</v>
+        <v>0.001024254796926138</v>
       </c>
       <c r="M5" t="n">
-        <v>10.27191665731237</v>
+        <v>10.19855178522155</v>
       </c>
       <c r="N5" t="n">
-        <v>218.6209881850674</v>
+        <v>216.9147211151819</v>
       </c>
       <c r="O5" t="n">
-        <v>14.78583741913414</v>
+        <v>14.72802502425841</v>
       </c>
       <c r="P5" t="n">
-        <v>298.0544197846595</v>
+        <v>298.0682451557404</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27789,28 +27999,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3911069683054371</v>
+        <v>0.4125683852402225</v>
       </c>
       <c r="J6" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K6" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="L6" t="n">
-        <v>0.014732116691344</v>
+        <v>0.01658374816939689</v>
       </c>
       <c r="M6" t="n">
-        <v>15.15481963156553</v>
+        <v>15.14845020512117</v>
       </c>
       <c r="N6" t="n">
-        <v>572.9391297509629</v>
+        <v>570.0354146253927</v>
       </c>
       <c r="O6" t="n">
-        <v>23.93614692783621</v>
+        <v>23.87541443881954</v>
       </c>
       <c r="P6" t="n">
-        <v>294.3222916191783</v>
+        <v>294.0858105298946</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27867,28 +28077,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2491133473796667</v>
+        <v>-0.2255439910023253</v>
       </c>
       <c r="J7" t="n">
+        <v>383</v>
+      </c>
+      <c r="K7" t="n">
         <v>380</v>
       </c>
-      <c r="K7" t="n">
-        <v>377</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0189426899195233</v>
+        <v>0.01567108964461039</v>
       </c>
       <c r="M7" t="n">
-        <v>10.20027729547187</v>
+        <v>10.24299926001441</v>
       </c>
       <c r="N7" t="n">
-        <v>175.8439357406296</v>
+        <v>176.3085723872981</v>
       </c>
       <c r="O7" t="n">
-        <v>13.26061596384684</v>
+        <v>13.27812382783419</v>
       </c>
       <c r="P7" t="n">
-        <v>323.2442602132607</v>
+        <v>322.9805882426307</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27945,28 +28155,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1802130978914779</v>
+        <v>-0.1654888709567467</v>
       </c>
       <c r="J8" t="n">
+        <v>383</v>
+      </c>
+      <c r="K8" t="n">
         <v>380</v>
       </c>
-      <c r="K8" t="n">
-        <v>377</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01323458029275904</v>
+        <v>0.01130506277371457</v>
       </c>
       <c r="M8" t="n">
-        <v>8.863727449144763</v>
+        <v>8.855593417010976</v>
       </c>
       <c r="N8" t="n">
-        <v>132.4820762874086</v>
+        <v>132.1590107319055</v>
       </c>
       <c r="O8" t="n">
-        <v>11.51008585056639</v>
+        <v>11.49604326418031</v>
       </c>
       <c r="P8" t="n">
-        <v>317.8310385223839</v>
+        <v>317.6663178319952</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28023,28 +28233,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1897348360546049</v>
+        <v>-0.1736851102571482</v>
       </c>
       <c r="J9" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K9" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01403861389379779</v>
+        <v>0.01192702767608056</v>
       </c>
       <c r="M9" t="n">
-        <v>8.766958003511414</v>
+        <v>8.774386802219837</v>
       </c>
       <c r="N9" t="n">
-        <v>139.6394591113744</v>
+        <v>139.1965865180916</v>
       </c>
       <c r="O9" t="n">
-        <v>11.81691411119563</v>
+        <v>11.79816030227135</v>
       </c>
       <c r="P9" t="n">
-        <v>315.6441676072116</v>
+        <v>315.465641454663</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28101,28 +28311,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2798718740312132</v>
+        <v>-0.2557501771063084</v>
       </c>
       <c r="J10" t="n">
+        <v>383</v>
+      </c>
+      <c r="K10" t="n">
         <v>380</v>
       </c>
-      <c r="K10" t="n">
-        <v>377</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.0396761918450762</v>
+        <v>0.03334840015849172</v>
       </c>
       <c r="M10" t="n">
-        <v>7.809441095293547</v>
+        <v>7.850533745544425</v>
       </c>
       <c r="N10" t="n">
-        <v>103.725825253593</v>
+        <v>104.6156643209295</v>
       </c>
       <c r="O10" t="n">
-        <v>10.18458763296742</v>
+        <v>10.22817991242477</v>
       </c>
       <c r="P10" t="n">
-        <v>315.59112688589</v>
+        <v>315.3211562294402</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28179,28 +28389,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1359199781610686</v>
+        <v>-0.1085783292666577</v>
       </c>
       <c r="J11" t="n">
+        <v>383</v>
+      </c>
+      <c r="K11" t="n">
         <v>380</v>
       </c>
-      <c r="K11" t="n">
-        <v>377</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.00679954444414832</v>
+        <v>0.004353699464108796</v>
       </c>
       <c r="M11" t="n">
-        <v>9.449824673983704</v>
+        <v>9.494261142222513</v>
       </c>
       <c r="N11" t="n">
-        <v>147.6401093233859</v>
+        <v>148.7656994325106</v>
       </c>
       <c r="O11" t="n">
-        <v>12.15072464190453</v>
+        <v>12.19695451465285</v>
       </c>
       <c r="P11" t="n">
-        <v>313.1148909022636</v>
+        <v>312.8089307910699</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28257,28 +28467,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1855165789734581</v>
+        <v>-0.1572031797085734</v>
       </c>
       <c r="J12" t="n">
+        <v>383</v>
+      </c>
+      <c r="K12" t="n">
         <v>380</v>
       </c>
-      <c r="K12" t="n">
-        <v>377</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.008573218732523702</v>
+        <v>0.006195616042922181</v>
       </c>
       <c r="M12" t="n">
-        <v>10.79794637011535</v>
+        <v>10.83630381355168</v>
       </c>
       <c r="N12" t="n">
-        <v>217.7523591405046</v>
+        <v>218.7302885430285</v>
       </c>
       <c r="O12" t="n">
-        <v>14.75643449958372</v>
+        <v>14.78953307386777</v>
       </c>
       <c r="P12" t="n">
-        <v>310.2890515466651</v>
+        <v>309.9723334324974</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28335,28 +28545,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1300512758870407</v>
+        <v>-0.09445909701137456</v>
       </c>
       <c r="J13" t="n">
+        <v>383</v>
+      </c>
+      <c r="K13" t="n">
         <v>380</v>
       </c>
-      <c r="K13" t="n">
-        <v>377</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.003365624049733618</v>
+        <v>0.001780036324333212</v>
       </c>
       <c r="M13" t="n">
-        <v>12.40764584230765</v>
+        <v>12.43661561566931</v>
       </c>
       <c r="N13" t="n">
-        <v>274.0186785671769</v>
+        <v>276.0926381210878</v>
       </c>
       <c r="O13" t="n">
-        <v>16.55350955438686</v>
+        <v>16.61603557173274</v>
       </c>
       <c r="P13" t="n">
-        <v>320.1130764390716</v>
+        <v>319.7149277182413</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28413,28 +28623,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08487009919413489</v>
+        <v>0.09013998879699793</v>
       </c>
       <c r="J14" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K14" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00317452629987458</v>
+        <v>0.003634786327096684</v>
       </c>
       <c r="M14" t="n">
-        <v>8.300330431773716</v>
+        <v>8.252738159449017</v>
       </c>
       <c r="N14" t="n">
-        <v>124.1373930988654</v>
+        <v>123.2801113111331</v>
       </c>
       <c r="O14" t="n">
-        <v>11.14169614999734</v>
+        <v>11.10315771801577</v>
       </c>
       <c r="P14" t="n">
-        <v>327.3421668319184</v>
+        <v>327.2832796600555</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28491,28 +28701,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3004212579389687</v>
+        <v>0.3078275760112498</v>
       </c>
       <c r="J15" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K15" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04557702505425565</v>
+        <v>0.04840225977503421</v>
       </c>
       <c r="M15" t="n">
-        <v>7.791572693318404</v>
+        <v>7.761222746752944</v>
       </c>
       <c r="N15" t="n">
-        <v>103.6757647857416</v>
+        <v>103.0639383659623</v>
       </c>
       <c r="O15" t="n">
-        <v>10.18212967830117</v>
+        <v>10.1520410935911</v>
       </c>
       <c r="P15" t="n">
-        <v>324.7938953979756</v>
+        <v>324.7111687143083</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28569,28 +28779,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2302843393775278</v>
+        <v>0.2492049224615857</v>
       </c>
       <c r="J16" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K16" t="n">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02320687066212335</v>
+        <v>0.02724598701392233</v>
       </c>
       <c r="M16" t="n">
-        <v>8.563714654998655</v>
+        <v>8.589241466459042</v>
       </c>
       <c r="N16" t="n">
-        <v>120.8294275103662</v>
+        <v>121.0501019295499</v>
       </c>
       <c r="O16" t="n">
-        <v>10.99224397065341</v>
+        <v>11.00227712473876</v>
       </c>
       <c r="P16" t="n">
-        <v>328.7102185334364</v>
+        <v>328.4968653841881</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28647,28 +28857,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1646731702110052</v>
+        <v>0.1910044208605207</v>
       </c>
       <c r="J17" t="n">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K17" t="n">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01164395215918224</v>
+        <v>0.01556734185724262</v>
       </c>
       <c r="M17" t="n">
-        <v>8.863480955257668</v>
+        <v>8.933626670652584</v>
       </c>
       <c r="N17" t="n">
-        <v>128.3429039512996</v>
+        <v>129.7170082002818</v>
       </c>
       <c r="O17" t="n">
-        <v>11.3288527199933</v>
+        <v>11.38933747854904</v>
       </c>
       <c r="P17" t="n">
-        <v>336.1767834842469</v>
+        <v>335.8856240850316</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28706,7 +28916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R381"/>
+  <dimension ref="A1:R384"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63501,7 +63711,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>-38.22453912731617,174.71323681367977</t>
+          <t>-38.224527444956166,174.71316768221945</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -63536,17 +63746,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>-38.21966197315196,174.71436087637935</t>
+          <t>-38.21965729775928,174.7144375099455</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>-38.218959799299206,174.7142681551022</t>
+          <t>-38.21895448483925,174.71435526375024</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>-38.21825763942593,174.7141750928794</t>
+          <t>-38.21825348517571,174.7142431850066</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -63580,6 +63790,282 @@
         </is>
       </c>
       <c r="R381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:59+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-38.22452995506285,174.71318253598866</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-38.22391405817701,174.7138092666179</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-38.22324280053448,174.71410843049958</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-38.22257255519959,174.7144136232794</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-38.22184883869208,174.71440242857668</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-38.221105147753434,174.7144582478763</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>-38.22036347192862,174.71452548087217</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>-38.21965609590436,174.714457209211</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>-38.2189538318162,174.7143659672955</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>-38.21825204020989,174.71426686922263</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>-38.21754011953214,174.71425938653118</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>-38.216848796517475,174.71398189608797</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>-38.21613999308437,174.7139510010101</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>-38.215442926714665,174.7138057972589</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>-38.21474970832919,174.71362023353637</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>-38.21406005622387,174.71339725863453</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:55+00:00</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>-38.22452995506285,174.71318253598866</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>-38.22391405817701,174.7138092666179</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>-38.22324280053448,174.71410843049958</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>-38.22257370639449,174.71442043574064</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-38.221845517192094,174.7143827731513</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>-38.22110441562161,174.71444652082326</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>-38.22036368375875,174.7145213781007</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>-38.21965665167582,174.71444809972417</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>-38.21895458904498,174.71435355573766</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>-38.2182521305204,174.71426538895915</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>-38.21754011953214,174.71425938653118</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>-38.21684602749976,174.7140124158692</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>-38.216135109434184,174.71400213328613</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>-38.21543858454108,174.71385126034465</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>-38.21474847391645,174.71363315808577</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>-38.214059103361706,174.713407235389</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:06:12+00:00</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>-38.2245300683007,174.71318320608356</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>-38.22391256725244,174.71380044376738</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>-38.22324247970608,174.71410653192817</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>-38.22257253632754,174.71441351159973</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-38.22184468681657,174.71437785929518</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-38.22110455778323,174.7144487979209</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>-38.220363754368755,174.7145200105102</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>-38.21965592222564,174.7144600559256</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>-38.21895379013385,174.71436665050052</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>-38.218251421929814,174.71427700333393</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>-38.21753699522185,174.71430191532275</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>-38.21684566721805,174.7140163868443</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>-38.216135261033415,174.71400054603157</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>-38.21543910430343,174.7138458183796</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>-38.21474826818087,174.71363531217727</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>-38.21405792311084,174.71341959295947</t>
+        </is>
+      </c>
+      <c r="R384" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0250/nzd0250.xlsx
+++ b/data/nzd0250/nzd0250.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R384"/>
+  <dimension ref="A1:R385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23415,6 +23415,66 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="n">
+        <v>359.2</v>
+      </c>
+      <c r="C385" t="n">
+        <v>317.28</v>
+      </c>
+      <c r="D385" t="n">
+        <v>310.82</v>
+      </c>
+      <c r="E385" t="n">
+        <v>300.68</v>
+      </c>
+      <c r="F385" t="n">
+        <v>320.16</v>
+      </c>
+      <c r="G385" t="n">
+        <v>335.28</v>
+      </c>
+      <c r="H385" t="n">
+        <v>324.29</v>
+      </c>
+      <c r="I385" t="n">
+        <v>323.04</v>
+      </c>
+      <c r="J385" t="n">
+        <v>327.16</v>
+      </c>
+      <c r="K385" t="n">
+        <v>331.53</v>
+      </c>
+      <c r="L385" t="n">
+        <v>323.39</v>
+      </c>
+      <c r="M385" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="N385" t="n">
+        <v>329.91</v>
+      </c>
+      <c r="O385" t="n">
+        <v>335.12</v>
+      </c>
+      <c r="P385" t="n">
+        <v>347.49</v>
+      </c>
+      <c r="Q385" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23426,7 +23486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B409"/>
+  <dimension ref="A1:B411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27519,6 +27579,26 @@
       </c>
       <c r="B409" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B410" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B411" t="n">
+        <v>1.57</v>
       </c>
     </row>
   </sheetData>
@@ -27687,28 +27767,28 @@
         <v>0.0437</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008468362930902454</v>
+        <v>0.01428512953899763</v>
       </c>
       <c r="J2" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K2" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L2" t="n">
-        <v>4.11634419776874e-05</v>
+        <v>0.0001173315292981592</v>
       </c>
       <c r="M2" t="n">
-        <v>7.788792142276868</v>
+        <v>7.799141675289849</v>
       </c>
       <c r="N2" t="n">
-        <v>97.03222283920763</v>
+        <v>97.12858022833846</v>
       </c>
       <c r="O2" t="n">
-        <v>9.85049353277325</v>
+        <v>9.855383312095906</v>
       </c>
       <c r="P2" t="n">
-        <v>347.3531042057033</v>
+        <v>347.2883172591104</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27765,28 +27845,28 @@
         <v>0.0645</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0199360353549694</v>
+        <v>-0.01950580921841581</v>
       </c>
       <c r="J3" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K3" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004592952850019927</v>
+        <v>0.0004420472051314128</v>
       </c>
       <c r="M3" t="n">
-        <v>5.313460335921629</v>
+        <v>5.301496201171982</v>
       </c>
       <c r="N3" t="n">
-        <v>48.17621797752595</v>
+        <v>48.05201892871262</v>
       </c>
       <c r="O3" t="n">
-        <v>6.940909016658117</v>
+        <v>6.931956356521052</v>
       </c>
       <c r="P3" t="n">
-        <v>316.9631633991543</v>
+        <v>316.9583715552296</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27843,28 +27923,28 @@
         <v>0.0994</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2646337492100172</v>
+        <v>-0.2596924499832766</v>
       </c>
       <c r="J4" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K4" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04121431705314738</v>
+        <v>0.03985042841788922</v>
       </c>
       <c r="M4" t="n">
-        <v>6.759778957323602</v>
+        <v>6.771952742148708</v>
       </c>
       <c r="N4" t="n">
-        <v>89.89463079220376</v>
+        <v>89.9081222105025</v>
       </c>
       <c r="O4" t="n">
-        <v>9.48127790923796</v>
+        <v>9.481989359332909</v>
       </c>
       <c r="P4" t="n">
-        <v>308.1941696503703</v>
+        <v>308.1387866394146</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27921,28 +28001,28 @@
         <v>0.052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06258558242572268</v>
+        <v>0.06303593977234298</v>
       </c>
       <c r="J5" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K5" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001024254796926138</v>
+        <v>0.001044572887354378</v>
       </c>
       <c r="M5" t="n">
-        <v>10.19855178522155</v>
+        <v>10.17419968645613</v>
       </c>
       <c r="N5" t="n">
-        <v>216.9147211151819</v>
+        <v>216.3519986157801</v>
       </c>
       <c r="O5" t="n">
-        <v>14.72802502425841</v>
+        <v>14.70890881798443</v>
       </c>
       <c r="P5" t="n">
-        <v>298.0682451557404</v>
+        <v>298.0632939860346</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27999,28 +28079,28 @@
         <v>0.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4125683852402225</v>
+        <v>0.4199487926153335</v>
       </c>
       <c r="J6" t="n">
+        <v>384</v>
+      </c>
+      <c r="K6" t="n">
         <v>383</v>
       </c>
-      <c r="K6" t="n">
-        <v>382</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.01658374816939689</v>
+        <v>0.01724531984428079</v>
       </c>
       <c r="M6" t="n">
-        <v>15.14845020512117</v>
+        <v>15.14855445498478</v>
       </c>
       <c r="N6" t="n">
-        <v>570.0354146253927</v>
+        <v>569.1230168127752</v>
       </c>
       <c r="O6" t="n">
-        <v>23.87541443881954</v>
+        <v>23.85629931093201</v>
       </c>
       <c r="P6" t="n">
-        <v>294.0858105298946</v>
+        <v>294.0043323524427</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28077,28 +28157,28 @@
         <v>0.0743</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2255439910023253</v>
+        <v>-0.2162558217403552</v>
       </c>
       <c r="J7" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K7" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01567108964461039</v>
+        <v>0.01443091304170707</v>
       </c>
       <c r="M7" t="n">
-        <v>10.24299926001441</v>
+        <v>10.26485715610237</v>
       </c>
       <c r="N7" t="n">
-        <v>176.3085723872981</v>
+        <v>176.7271448505514</v>
       </c>
       <c r="O7" t="n">
-        <v>13.27812382783419</v>
+        <v>13.29387621615875</v>
       </c>
       <c r="P7" t="n">
-        <v>322.9805882426307</v>
+        <v>322.8764846948813</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28155,28 +28235,28 @@
         <v>0.0742</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1654888709567467</v>
+        <v>-0.1598841236311299</v>
       </c>
       <c r="J8" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K8" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01130506277371457</v>
+        <v>0.01059130142774545</v>
       </c>
       <c r="M8" t="n">
-        <v>8.855593417010976</v>
+        <v>8.856098950821469</v>
       </c>
       <c r="N8" t="n">
-        <v>132.1590107319055</v>
+        <v>132.1330500038005</v>
       </c>
       <c r="O8" t="n">
-        <v>11.49604326418031</v>
+        <v>11.49491409292825</v>
       </c>
       <c r="P8" t="n">
-        <v>317.6663178319952</v>
+        <v>317.6034987699843</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28233,28 +28313,28 @@
         <v>0.0598</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1736851102571482</v>
+        <v>-0.1675410456296747</v>
       </c>
       <c r="J9" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K9" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01192702767608056</v>
+        <v>0.01113556488105072</v>
       </c>
       <c r="M9" t="n">
-        <v>8.774386802219837</v>
+        <v>8.781247184603478</v>
       </c>
       <c r="N9" t="n">
-        <v>139.1965865180916</v>
+        <v>139.223104377199</v>
       </c>
       <c r="O9" t="n">
-        <v>11.79816030227135</v>
+        <v>11.79928406206067</v>
       </c>
       <c r="P9" t="n">
-        <v>315.465641454663</v>
+        <v>315.3972090739776</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28311,28 +28391,28 @@
         <v>0.06619999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2557501771063084</v>
+        <v>-0.2462822822118704</v>
       </c>
       <c r="J10" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K10" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03334840015849172</v>
+        <v>0.0309000337743579</v>
       </c>
       <c r="M10" t="n">
-        <v>7.850533745544425</v>
+        <v>7.87146233054502</v>
       </c>
       <c r="N10" t="n">
-        <v>104.6156643209295</v>
+        <v>105.2568443115432</v>
       </c>
       <c r="O10" t="n">
-        <v>10.22817991242477</v>
+        <v>10.25947583025289</v>
       </c>
       <c r="P10" t="n">
-        <v>315.3211562294402</v>
+        <v>315.2150382830043</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28389,28 +28469,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1085783292666577</v>
+        <v>-0.09764255607634978</v>
       </c>
       <c r="J11" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K11" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L11" t="n">
-        <v>0.004353699464108796</v>
+        <v>0.003513994507603591</v>
       </c>
       <c r="M11" t="n">
-        <v>9.494261142222513</v>
+        <v>9.517629430887986</v>
       </c>
       <c r="N11" t="n">
-        <v>148.7656994325106</v>
+        <v>149.5969666233229</v>
       </c>
       <c r="O11" t="n">
-        <v>12.19695451465285</v>
+        <v>12.23098387797657</v>
       </c>
       <c r="P11" t="n">
-        <v>312.8089307910699</v>
+        <v>312.6863605886562</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28467,28 +28547,28 @@
         <v>0.0489</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1572031797085734</v>
+        <v>-0.148282606362428</v>
       </c>
       <c r="J12" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K12" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L12" t="n">
-        <v>0.006195616042922181</v>
+        <v>0.005525423618786163</v>
       </c>
       <c r="M12" t="n">
-        <v>10.83630381355168</v>
+        <v>10.84825344476302</v>
       </c>
       <c r="N12" t="n">
-        <v>218.7302885430285</v>
+        <v>218.9691383602764</v>
       </c>
       <c r="O12" t="n">
-        <v>14.78953307386777</v>
+        <v>14.797605832035</v>
       </c>
       <c r="P12" t="n">
-        <v>309.9723334324974</v>
+        <v>309.8723499688998</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28545,28 +28625,28 @@
         <v>0.0409</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.09445909701137456</v>
+        <v>-0.08430762618656684</v>
       </c>
       <c r="J13" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K13" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L13" t="n">
-        <v>0.001780036324333212</v>
+        <v>0.001420757602807465</v>
       </c>
       <c r="M13" t="n">
-        <v>12.43661561566931</v>
+        <v>12.44063778662253</v>
       </c>
       <c r="N13" t="n">
-        <v>276.0926381210878</v>
+        <v>276.4207557747256</v>
       </c>
       <c r="O13" t="n">
-        <v>16.61603557173274</v>
+        <v>16.62590616401782</v>
       </c>
       <c r="P13" t="n">
-        <v>319.7149277182413</v>
+        <v>319.6011481242299</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28623,28 +28703,28 @@
         <v>0.0427</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09013998879699793</v>
+        <v>0.09023417355992178</v>
       </c>
       <c r="J14" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K14" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L14" t="n">
-        <v>0.003634786327096684</v>
+        <v>0.003661995316863398</v>
       </c>
       <c r="M14" t="n">
-        <v>8.252738159449017</v>
+        <v>8.231286961624438</v>
       </c>
       <c r="N14" t="n">
-        <v>123.2801113111331</v>
+        <v>122.9549249497327</v>
       </c>
       <c r="O14" t="n">
-        <v>11.10315771801577</v>
+        <v>11.08850417999347</v>
       </c>
       <c r="P14" t="n">
-        <v>327.2832796600555</v>
+        <v>327.2822247674274</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28701,28 +28781,28 @@
         <v>0.0682</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3078275760112498</v>
+        <v>0.3088789107547256</v>
       </c>
       <c r="J15" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K15" t="n">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L15" t="n">
-        <v>0.04840225977503421</v>
+        <v>0.04896321912965695</v>
       </c>
       <c r="M15" t="n">
-        <v>7.761222746752944</v>
+        <v>7.745222436584648</v>
       </c>
       <c r="N15" t="n">
-        <v>103.0639383659623</v>
+        <v>102.8040344643344</v>
       </c>
       <c r="O15" t="n">
-        <v>10.1520410935911</v>
+        <v>10.13923243960481</v>
       </c>
       <c r="P15" t="n">
-        <v>324.7111687143083</v>
+        <v>324.6994003770668</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28779,28 +28859,28 @@
         <v>0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2492049224615857</v>
+        <v>0.2554473470103495</v>
       </c>
       <c r="J16" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K16" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L16" t="n">
-        <v>0.02724598701392233</v>
+        <v>0.02864893066969709</v>
       </c>
       <c r="M16" t="n">
-        <v>8.589241466459042</v>
+        <v>8.597637619517474</v>
       </c>
       <c r="N16" t="n">
-        <v>121.0501019295499</v>
+        <v>121.1233544615691</v>
       </c>
       <c r="O16" t="n">
-        <v>11.00227712473876</v>
+        <v>11.00560559267727</v>
       </c>
       <c r="P16" t="n">
-        <v>328.4968653841881</v>
+        <v>328.4263385092084</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28857,28 +28937,28 @@
         <v>0.0585</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1910044208605207</v>
+        <v>0.1987352788853252</v>
       </c>
       <c r="J17" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K17" t="n">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01556734185724262</v>
+        <v>0.0168396618419151</v>
       </c>
       <c r="M17" t="n">
-        <v>8.933626670652584</v>
+        <v>8.951436770411718</v>
       </c>
       <c r="N17" t="n">
-        <v>129.7170082002818</v>
+        <v>130.0059442849368</v>
       </c>
       <c r="O17" t="n">
-        <v>11.38933747854904</v>
+        <v>11.40201492215024</v>
       </c>
       <c r="P17" t="n">
-        <v>335.8856240850316</v>
+        <v>335.7999704851979</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28916,7 +28996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R384"/>
+  <dimension ref="A1:R385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64071,6 +64151,98 @@
         </is>
       </c>
     </row>
+    <row r="385">
+      <c r="A385" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:04+00:00</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>-38.22452368922908,174.71314545740864</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>-38.22391464322317,174.7138127287492</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>-38.22323866750745,174.7140839724339</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>-38.222569630030385,174.71439631292796</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>-38.22184468681657,174.71437785929518</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-38.22110238981383,174.71441407218225</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>-38.220364601687564,174.714503599424</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>-38.21965597780284,174.71445914497693</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>-38.218954575150875,174.7143537834727</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>-38.21825333928996,174.71424557620156</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>-38.21753864927038,174.71427940008067</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>-38.216844009920536,174.71403465332904</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>-38.21613333355589,174.71402072683912</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>-38.215437328447706,174.71386441175986</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>-38.21474906946663,174.7136269225576</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>-38.21405728425891,174.71342628191942</t>
+        </is>
+      </c>
+      <c r="R385" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
